--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/VALSAD.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/VALSAD.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\GJ WP 2026-27\2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8100EEA-97F5-494F-A41B-2BD574792C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327B5B6F-F47A-4F47-9CD9-1FE7CE512DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
   <si>
     <t xml:space="preserve">                               GUJARAT                                              STATEMENT NO. 4                                                  CENTRAL                                                                                      </t>
   </si>
@@ -71,36 +71,6 @@
   </si>
   <si>
     <t>OS</t>
-  </si>
-  <si>
-    <t>Bavla</t>
-  </si>
-  <si>
-    <t>Devdholera</t>
-  </si>
-  <si>
-    <t>Dhandhuka</t>
-  </si>
-  <si>
-    <t>Parabdi</t>
-  </si>
-  <si>
-    <t>Mandal</t>
-  </si>
-  <si>
-    <t>Kunpur</t>
-  </si>
-  <si>
-    <t>Odaki</t>
-  </si>
-  <si>
-    <t>Viramgam</t>
-  </si>
-  <si>
-    <t>Dediyasan</t>
-  </si>
-  <si>
-    <t>Jaksi</t>
   </si>
   <si>
     <t>Total Part- A</t>
@@ -409,23 +379,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -728,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -760,16 +730,16 @@
       <c r="H2" s="14"/>
     </row>
     <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
+      <c r="A3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
@@ -777,16 +747,16 @@
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="13">
+        <v>17</v>
+      </c>
+      <c r="D4" s="11">
         <v>10</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13">
+      <c r="E4" s="11"/>
+      <c r="F4" s="11">
         <v>10</v>
       </c>
-      <c r="G4" s="13"/>
+      <c r="G4" s="11"/>
       <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
@@ -795,14 +765,14 @@
       <c r="A5" s="17"/>
       <c r="B5" s="18"/>
       <c r="C5" s="20"/>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12" t="s">
+      <c r="E5" s="13"/>
+      <c r="F5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="12"/>
+      <c r="G5" s="13"/>
       <c r="H5" s="2">
         <f>SUM(D4:G4)</f>
         <v>20</v>
@@ -833,394 +803,274 @@
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="1">
+        <f>SUM(D7:D9)</f>
+        <v>2</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <f>SUM(F7:F9)</f>
+        <v>4</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>5</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="4">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2">
+        <v>5</v>
+      </c>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="4">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2">
+        <v>4</v>
+      </c>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="4">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2">
+        <v>3</v>
+      </c>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="4">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="1">
+        <f>SUM(D12:D18)</f>
+        <v>8</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1">
+        <f t="shared" ref="F19" si="0">SUM(F12:F18)</f>
+        <v>6</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="4">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6">
-        <v>2</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1</v>
-      </c>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="6">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6">
-        <v>2</v>
-      </c>
-      <c r="G16" s="1">
-        <v>2</v>
-      </c>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="1">
-        <f>SUM(D14:D16)</f>
-        <v>2</v>
-      </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1">
-        <f>SUM(F14:F16)</f>
-        <v>4</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="4">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2">
-        <v>3</v>
-      </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D20" s="4">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2">
-        <v>5</v>
-      </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="4">
-        <v>2</v>
-      </c>
-      <c r="G21" s="2">
-        <v>5</v>
-      </c>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="4">
-        <v>2</v>
-      </c>
-      <c r="G22" s="2">
-        <v>4</v>
-      </c>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="2">
-        <v>4</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="4">
-        <v>2</v>
-      </c>
-      <c r="G24" s="2">
-        <v>3</v>
-      </c>
-      <c r="H24" s="6"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="4">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2">
-        <v>2</v>
-      </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="6"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="1">
-        <f>SUM(D19:D25)</f>
-        <v>8</v>
-      </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1">
-        <f t="shared" ref="F26" si="0">SUM(F19:F25)</f>
-        <v>6</v>
-      </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="1">
-        <f>+D17+D26</f>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="1">
+        <f>+D10+D19</f>
         <v>10</v>
       </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1">
-        <f>+F17+F26</f>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1">
+        <f>+F10+F19</f>
         <v>10</v>
       </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1">
+      <c r="G20" s="1"/>
+      <c r="H20" s="1">
         <v>20</v>
       </c>
     </row>
@@ -1233,10 +1083,10 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:G5"/>
   </mergeCells>
@@ -1246,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -1255,7 +1105,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -1278,33 +1128,33 @@
       <c r="H2" s="14"/>
     </row>
     <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
+      <c r="A3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
     </row>
     <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="13">
+        <v>17</v>
+      </c>
+      <c r="D4" s="11">
         <v>6</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13">
+      <c r="E4" s="11"/>
+      <c r="F4" s="11">
         <v>4</v>
       </c>
-      <c r="G4" s="13"/>
+      <c r="G4" s="11"/>
       <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1313,14 +1163,14 @@
       <c r="A5" s="17"/>
       <c r="B5" s="18"/>
       <c r="C5" s="20"/>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12" t="s">
+      <c r="E5" s="13"/>
+      <c r="F5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="12"/>
+      <c r="G5" s="13"/>
       <c r="H5" s="2">
         <f>SUM(D4:G4)</f>
         <v>10</v>
@@ -1350,279 +1200,159 @@
       </c>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="6">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="1">
+        <f>SUM(D7:D9)</f>
+        <v>6</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1">
+        <f>SUM(F7:F9)</f>
+        <v>2</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>2</v>
+      </c>
+      <c r="H12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="1">
+        <f>SUM(D12)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1">
+        <f t="shared" ref="F13" si="0">SUM(F12)</f>
+        <v>2</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="4">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="6">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="6">
-        <v>2</v>
-      </c>
-      <c r="G14" s="5">
-        <v>1</v>
-      </c>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="6">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1">
-        <v>2</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="6">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1">
-        <v>3</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="1">
-        <f>SUM(D14:D16)</f>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="1">
+        <f>+D10+D13</f>
         <v>6</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1">
-        <f>SUM(F14:F16)</f>
-        <v>2</v>
-      </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4">
-        <v>2</v>
-      </c>
-      <c r="G19" s="2">
-        <v>2</v>
-      </c>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="10"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="1">
-        <f>SUM(D19)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1">
-        <f t="shared" ref="F20" si="0">SUM(F19)</f>
-        <v>2</v>
-      </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="1">
-        <f>+D17+D20</f>
-        <v>6</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1">
-        <f>+F17+F20</f>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1">
+        <f>+F10+F13</f>
         <v>4</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1">
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
         <v>10</v>
       </c>
     </row>
@@ -1635,12 +1365,12 @@
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A10:C10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
